--- a/files_result_14.07.2025/Электричество 2025.xlsx
+++ b/files_result_14.07.2025/Электричество 2025.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A976C48-CD62-4331-AFAC-90CAA3A77A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1ACFDD-29CF-403C-B8E2-45E2B19EC73F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -178,15 +178,14 @@
     <t>стоимость</t>
   </si>
   <si>
-    <t>02.06.2025</t>
+    <t>20.05.2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;₽&quot;;\-#,##0.00\ &quot;₽&quot;"/>
+  <numFmts count="2">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;₽&quot;;[Red]\-#,##0.00\ &quot;₽&quot;"/>
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
@@ -689,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -795,7 +794,6 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="7" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5433,12 +5431,10 @@
       <c r="E179" s="9"/>
       <c r="F179" s="6"/>
       <c r="G179" s="6"/>
-      <c r="H179" s="54">
-        <v>1</v>
-      </c>
+      <c r="H179" s="54"/>
       <c r="I179" s="8">
         <f t="shared" si="9"/>
-        <v>-160309.9470000001</v>
+        <v>-160308.9470000001</v>
       </c>
       <c r="J179" s="6">
         <v>0</v>
@@ -5448,9 +5444,7 @@
       </c>
       <c r="L179" s="54"/>
       <c r="M179" s="6"/>
-      <c r="N179" s="87">
-        <v>1</v>
-      </c>
+      <c r="N179" s="6"/>
       <c r="O179" s="6"/>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
